--- a/Data_for_analysis.xlsx
+++ b/Data_for_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ohsuitg-my.sharepoint.com/personal/hutchenm_ohsu_edu/Documents/From_Box/Hutch Lab Common Folder/Publications_Presentations/Manuscripts/draft manuscripts/hPTEC paper/hPTEC_DA_draft/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ohsuitg-my.sharepoint.com/personal/hutchenm_ohsu_edu/Documents/From_Box/Hutch Lab Common Folder/Publications_Presentations/Manuscripts/HPTEC_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="820" documentId="11_F25DC773A252ABDACC10489AB9DA5E985BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2BD9981-6983-46FA-95C9-C83651B6CBF8}"/>
+  <xr:revisionPtr revIDLastSave="851" documentId="11_F25DC773A252ABDACC10489AB9DA5E985BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24885A4B-8960-4ED9-9700-428637402B4E}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="3345" windowWidth="21600" windowHeight="11295" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mb1" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,16 @@
     <sheet name="Cil" sheetId="6" r:id="rId4"/>
     <sheet name="siRNA_qPCR" sheetId="8" r:id="rId5"/>
     <sheet name="LRP2WB" sheetId="9" r:id="rId6"/>
-    <sheet name="siRNA" sheetId="5" r:id="rId7"/>
-    <sheet name="VCAM1WB" sheetId="7" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId9"/>
+    <sheet name="LRP2_passWB" sheetId="12" r:id="rId7"/>
+    <sheet name="AQP1WB" sheetId="11" r:id="rId8"/>
+    <sheet name="siRNA" sheetId="5" r:id="rId9"/>
+    <sheet name="VCAM1WB" sheetId="7" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Cil!$A$1:$F$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyna!$A$1:$F$318</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">siRNA!$A$1:$F$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">siRNA!$A$1:$F$471</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="271">
   <si>
     <t>comment</t>
   </si>
@@ -817,6 +819,51 @@
   </si>
   <si>
     <t>LRP2-WB</t>
+  </si>
+  <si>
+    <t>AQP1-WB</t>
+  </si>
+  <si>
+    <t>20260320 WB</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>NHK_p2_1</t>
+  </si>
+  <si>
+    <t>NHK_p2_2</t>
+  </si>
+  <si>
+    <t>NHK_p2_3</t>
+  </si>
+  <si>
+    <t>NHK_p3_1</t>
+  </si>
+  <si>
+    <t>NHK_p3_2</t>
+  </si>
+  <si>
+    <t>NHK_p3_3</t>
+  </si>
+  <si>
+    <t>NHK_p4_1</t>
+  </si>
+  <si>
+    <t>NHK_p4_2</t>
+  </si>
+  <si>
+    <t>NHK_p4_3</t>
+  </si>
+  <si>
+    <t>LRP2_pass-WB</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p4</t>
   </si>
 </sst>
 </file>
@@ -1606,6 +1653,220 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A1D441-C179-4F14-BD89-EA707BD31DF5}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2">
+        <v>0.86981657753010821</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3">
+        <v>1.0978829065893771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4">
+        <v>0.75433130501105694</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5">
+        <v>0.95980977113961319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6">
+        <v>0.86533364100271926</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7">
+        <v>1.0914323152547429</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8">
+        <v>1.1433476773436373</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9">
+        <v>1.0022548379984551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10">
+        <v>1.1324115209988255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>5.5267327285264858E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14">
+        <v>0.22107459674868021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15">
+        <v>0.64324160017119159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068F4625-A59D-4A49-9A11-71FFA5F2FE4D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{597E58D0-78EB-4E52-B792-B10679DE7A11}">
   <dimension ref="A1:F76"/>
@@ -12200,6 +12461,303 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0613ECBF-1E28-41DF-BA47-D32A32FB15AF}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2">
+        <v>0.89499270172725742</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3">
+        <v>0.95481768727722738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4">
+        <v>1.150189610995515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5">
+        <v>0.95824178508137425</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6">
+        <v>1.0363696852110196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" t="s">
+        <v>269</v>
+      </c>
+      <c r="F7">
+        <v>0.87663282723547331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" t="s">
+        <v>270</v>
+      </c>
+      <c r="F8">
+        <v>0.75387426460138818</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F9">
+        <v>0.75175601535472214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10">
+        <v>1.027209160571344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA84DBDD-BD2E-4CD3-A5DD-0D82FF63C434}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2">
+        <v>0.93800092749314146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3">
+        <v>0.98704696734044894</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4">
+        <v>1.3448430924134775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5">
+        <v>1.1117498948263984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6">
+        <v>0.99548963783453293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7">
+        <v>0.89276046733906866</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>0.72710514669311088</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>0.7378385140706134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>0.82963339164843242</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD12FE7-6F77-4065-BD28-1792EB842130}">
   <dimension ref="A1:F471"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22544,218 +23102,4 @@
   <autoFilter ref="A1:F471" xr:uid="{CBD12FE7-6F77-4065-BD28-1792EB842130}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A1D441-C179-4F14-BD89-EA707BD31DF5}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F2">
-        <v>0.86981657753010821</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F3">
-        <v>1.0978829065893771</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F4">
-        <v>0.75433130501105694</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5">
-        <v>0.95980977113961319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6">
-        <v>0.86533364100271926</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7">
-        <v>1.0914323152547429</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>218</v>
-      </c>
-      <c r="B8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F8">
-        <v>1.1433476773436373</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9">
-        <v>1.0022548379984551</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10">
-        <v>1.1324115209988255</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>5.5267327285264858E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" t="s">
-        <v>231</v>
-      </c>
-      <c r="F14">
-        <v>0.22107459674868021</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>232</v>
-      </c>
-      <c r="F15">
-        <v>0.64324160017119159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>227</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068F4625-A59D-4A49-9A11-71FFA5F2FE4D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>